--- a/construction_template/data/templates_blank/invoice_detail.xlsx
+++ b/construction_template/data/templates_blank/invoice_detail.xlsx
@@ -1522,8 +1522,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>2</v>
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ${authorityName}</t>
+        </is>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
